--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487758_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487758_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3332</v>
+        <v>3.4289</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8848</v>
+        <v>3.8442</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5516</v>
+        <v>-0.4153</v>
       </c>
       <c r="G2" t="n">
         <v>3.0009</v>
@@ -610,13 +610,13 @@
         <v>1.5523</v>
       </c>
       <c r="S2" t="n">
-        <v>0.674</v>
+        <v>-0.2302</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1541</v>
+        <v>0.1135</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.48</v>
+        <v>-0.3437</v>
       </c>
       <c r="V2" t="n">
         <v>-0.894</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9893</v>
+        <v>3.2262</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0442</v>
+        <v>3.4446</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0549</v>
+        <v>-0.2184</v>
       </c>
       <c r="G3" t="n">
         <v>2.8528</v>
@@ -688,13 +688,13 @@
         <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5218</v>
+        <v>-0.2849</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2894</v>
+        <v>0.111</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2324</v>
+        <v>-0.3959</v>
       </c>
       <c r="V3" t="n">
         <v>-0.894</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3644</v>
+        <v>2.8253</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2709</v>
+        <v>1.7319</v>
       </c>
       <c r="F4" t="n">
         <v>1.0935</v>
@@ -766,10 +766,10 @@
         <v>1.7463</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2248</v>
+        <v>-0.7638</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4229</v>
+        <v>0.0381</v>
       </c>
       <c r="U4" t="n">
         <v>-0.8018999999999999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.221</v>
+        <v>1.1938</v>
       </c>
       <c r="E5" t="n">
         <v>-0.9199000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1409</v>
+        <v>2.1137</v>
       </c>
       <c r="G5" t="n">
         <v>0.536</v>
@@ -844,13 +844,13 @@
         <v>0.9702</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2851</v>
+        <v>-0.3124</v>
       </c>
       <c r="T5" t="n">
         <v>0.0617</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3468</v>
+        <v>-0.374</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. VILA DE MIGUEL</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2177</v>
+        <v>-0.3389</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5389</v>
+        <v>2.3447</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3212</v>
+        <v>-2.6837</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1699</v>
+        <v>1.854</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4368</v>
+        <v>0.0799</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2669</v>
+        <v>1.774</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.6312</v>
+        <v>3.2917</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.6312</v>
+        <v>1.4953</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.7963</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4614</v>
+        <v>-1.4377</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1944</v>
+        <v>-1.4154</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2669</v>
+        <v>-0.0223</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3881</v>
+        <v>0.5821</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3881</v>
+        <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1283</v>
+        <v>-0.3272</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0924</v>
+        <v>0.0232</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0359</v>
+        <v>-0.3505</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5642</v>
+        <v>-2.4477</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5642</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3168</v>
+        <v>-0.6744</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2989</v>
+        <v>-0.4386</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0178</v>
+        <v>-0.2359</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0535</v>
@@ -1000,13 +1000,13 @@
         <v>1.7463</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1454</v>
+        <v>-0.503</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5607</v>
+        <v>0.4211</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.9241</v>
       </c>
       <c r="V7" t="n">
         <v>0.3299</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
+          <t>C. VILA DE MIGUEL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2974</v>
+        <v>-0.8183</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06279999999999999</v>
+        <v>-1.1394</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3601</v>
+        <v>0.3212</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2083</v>
+        <v>-1.1699</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9674</v>
+        <v>-1.4368</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7591</v>
+        <v>0.2669</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7885</v>
+        <v>-1.6312</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7579</v>
+        <v>-1.6312</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0305</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4198</v>
+        <v>0.4614</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2095</v>
+        <v>0.1944</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7897</v>
+        <v>0.2669</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1642</v>
+        <v>0.3881</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0294</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0453</v>
+        <v>0.4918</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0747</v>
+        <v>0.0359</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2239</v>
+        <v>-0.5642</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2239</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3037</v>
+        <v>-1.4525</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2436</v>
+        <v>-0.3376</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5474</v>
+        <v>-1.1148</v>
       </c>
       <c r="G9" t="n">
-        <v>1.854</v>
+        <v>-1.2083</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0799</v>
+        <v>-1.9674</v>
       </c>
       <c r="I9" t="n">
-        <v>1.774</v>
+        <v>0.7591</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2917</v>
+        <v>-0.7885</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4953</v>
+        <v>-0.7579</v>
       </c>
       <c r="L9" t="n">
-        <v>1.7963</v>
+        <v>-0.0305</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4377</v>
+        <v>-0.4198</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4154</v>
+        <v>-1.2095</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0223</v>
+        <v>0.7897</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.292</v>
+        <v>-0.1845</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0779</v>
+        <v>0.6449</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2142</v>
+        <v>-0.8294</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4477</v>
+        <v>-1.2239</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4477</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3938</v>
+        <v>-1.6964</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1102</v>
+        <v>-1.5491</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2836</v>
+        <v>-0.1473</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4841</v>
@@ -1234,13 +1234,13 @@
         <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3156</v>
+        <v>-0.6183</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6662</v>
+        <v>-0.1052</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6494</v>
+        <v>-0.5131</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5642</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. PEREZ CONTI</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9425</v>
+        <v>-3.8236</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3692</v>
+        <v>-3.184</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5733</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4764</v>
+        <v>-1.4926</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1897</v>
+        <v>-0.5355</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2867</v>
+        <v>-0.9571</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5717</v>
+        <v>-2.4651</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2471</v>
+        <v>-1.2523</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3246</v>
+        <v>-1.2129</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9046</v>
+        <v>0.9725</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9425</v>
+        <v>0.7168</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9621</v>
+        <v>0.2558</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.3582</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9403</v>
+        <v>-0.194</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9403</v>
+        <v>1.5523</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0502</v>
+        <v>-0.8639</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5309</v>
+        <v>-0.1472</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4807</v>
+        <v>-0.7167</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5164</v>
+        <v>-2.8254</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6119</v>
+        <v>-0.3776</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1283</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>A. PEREZ CONTI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6939</v>
+        <v>-3.8251</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9453</v>
+        <v>-2.17</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7486</v>
+        <v>-1.6551</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4926</v>
+        <v>-3.4764</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5355</v>
+        <v>-1.1897</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9571</v>
+        <v>-2.2867</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4651</v>
+        <v>-1.5717</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2523</v>
+        <v>-0.2471</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2129</v>
+        <v>-1.3246</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9725</v>
+        <v>-1.9046</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7168</v>
+        <v>-0.9425</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2558</v>
+        <v>-0.9621</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3582</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.194</v>
+        <v>-1.9403</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5523</v>
+        <v>1.9403</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7342</v>
+        <v>0.1677</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9085</v>
+        <v>0.7301</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8257</v>
+        <v>-0.5624</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.8254</v>
+        <v>-0.5164</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3776</v>
+        <v>0.6119</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4477</v>
+        <v>-1.1283</v>
       </c>
     </row>
     <row r="13">
@@ -1423,34 +1423,34 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.257900000000001</v>
+        <v>-1.955000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3239</v>
+        <v>1.626799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.581700000000001</v>
+        <v>-3.5817</v>
       </c>
       <c r="G13" t="n">
         <v>-1.498299999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4202999999999998</v>
+        <v>0.4202999999999995</v>
       </c>
       <c r="I13" t="n">
         <v>-1.9184</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1604000000000005</v>
+        <v>0.1604000000000003</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9136</v>
+        <v>3.913599999999999</v>
       </c>
       <c r="L13" t="n">
         <v>-3.7533</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.658399999999999</v>
+        <v>-1.6584</v>
       </c>
       <c r="N13" t="n">
         <v>-3.4934</v>
@@ -1468,13 +1468,13 @@
         <v>15.5228</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.6958</v>
+        <v>-3.3928</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0802</v>
+        <v>2.383</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.776</v>
+        <v>-5.7758</v>
       </c>
       <c r="V13" t="n">
         <v>-8.7059</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8739</v>
+        <v>6.4816</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9004</v>
+        <v>6.0015</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9735</v>
+        <v>0.4801</v>
       </c>
       <c r="G14" t="n">
         <v>4.2108</v>
@@ -1546,13 +1546,13 @@
         <v>0.5821</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3965</v>
+        <v>0.2112</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7020999999999999</v>
+        <v>0.399</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3056</v>
+        <v>-0.1878</v>
       </c>
       <c r="V14" t="n">
         <v>2.4477</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5203</v>
+        <v>5.1298</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8924</v>
+        <v>3.3929</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6279</v>
+        <v>1.7369</v>
       </c>
       <c r="G15" t="n">
         <v>3.6667</v>
@@ -1624,13 +1624,13 @@
         <v>0.5821</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3524</v>
+        <v>0.2571</v>
       </c>
       <c r="T15" t="n">
-        <v>0.074</v>
+        <v>0.5745</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4264</v>
+        <v>-0.3174</v>
       </c>
       <c r="V15" t="n">
         <v>1.788</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. MEJÍA ACOSTA</t>
+          <t>J. GONZÁLEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3394</v>
+        <v>3.0705</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0016</v>
+        <v>1.7069</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3378</v>
+        <v>1.3636</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2247</v>
+        <v>2.7526</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8966</v>
+        <v>0.061</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6718</v>
+        <v>2.6916</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6784</v>
+        <v>2.2756</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8506</v>
+        <v>-0.3048</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.1723</v>
+        <v>2.5804</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4536</v>
+        <v>0.477</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9540999999999999</v>
+        <v>0.3658</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5004</v>
+        <v>0.1112</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.1344</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9105</v>
+        <v>-1.1642</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7761</v>
+        <v>0.3881</v>
       </c>
       <c r="S16" t="n">
-        <v>4.5789</v>
+        <v>1.0941</v>
       </c>
       <c r="T16" t="n">
-        <v>4.5636</v>
+        <v>0.5955</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0153</v>
+        <v>0.4986</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GONZÁLEZ CHÁVEZ</t>
+          <t>A. GASE SECO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9154</v>
+        <v>1.1995</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3065</v>
+        <v>0.2864</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6089</v>
+        <v>0.9131</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7526</v>
+        <v>0.5595</v>
       </c>
       <c r="H17" t="n">
-        <v>0.061</v>
+        <v>0.0824</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6916</v>
+        <v>0.4771</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2756</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3048</v>
+        <v>1.3759</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5804</v>
+        <v>-0.4237</v>
       </c>
       <c r="M17" t="n">
-        <v>0.477</v>
+        <v>-0.3927</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3658</v>
+        <v>-1.2935</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1112</v>
+        <v>0.9008</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7761</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1642</v>
+        <v>-1.9403</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3881</v>
+        <v>0.5821</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9177</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1951</v>
+        <v>0.8538</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7439</v>
+        <v>0.064</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.0806</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.4208</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GASE SECO</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2385</v>
+        <v>0.764</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1863</v>
+        <v>1.6573</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0522</v>
+        <v>-0.8934</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5595</v>
+        <v>-3.5323</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0824</v>
+        <v>0.0585</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4771</v>
+        <v>-3.5908</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9520999999999999</v>
+        <v>-3.5308</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3759</v>
+        <v>-0.2348</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4237</v>
+        <v>-3.2961</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3927</v>
+        <v>-0.0015</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2935</v>
+        <v>0.2933</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9008</v>
+        <v>-0.2948</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9403</v>
+        <v>-0.194</v>
       </c>
       <c r="R18" t="n">
         <v>0.5821</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9567</v>
+        <v>0.2366</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7537</v>
+        <v>0.4867</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2031</v>
+        <v>-0.2501</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0806</v>
+        <v>3.6716</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4208</v>
+        <v>4.8955</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6597</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>G. MEJÍA ACOSTA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7098</v>
+        <v>0.5794</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4561</v>
+        <v>0.2989</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1659</v>
+        <v>0.2805</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.5323</v>
+        <v>1.2247</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0585</v>
+        <v>1.8966</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.5908</v>
+        <v>-0.6718</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.5308</v>
+        <v>1.6784</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2348</v>
+        <v>2.8506</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.2961</v>
+        <v>-1.1723</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0015</v>
+        <v>-0.4536</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2933</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2948</v>
+        <v>0.5004</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3881</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.194</v>
+        <v>-2.9105</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2371</v>
+        <v>1.8189</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7145</v>
+        <v>1.8609</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5226</v>
+        <v>-0.042</v>
       </c>
       <c r="V19" t="n">
-        <v>3.6716</v>
+        <v>-0.3299</v>
       </c>
       <c r="W19" t="n">
-        <v>4.8955</v>
+        <v>-0.3299</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>A. JIMÉNEZ BARRETO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9595</v>
+        <v>-1.4383</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0861</v>
+        <v>-1.5432</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8734</v>
+        <v>0.1049</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4798</v>
+        <v>-2.2469</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5067</v>
+        <v>-0.0948</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9865</v>
+        <v>-2.1522</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1252</v>
+        <v>-2.6075</v>
       </c>
       <c r="K20" t="n">
         <v>-0.6055</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7307</v>
+        <v>-2.002</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3546</v>
+        <v>0.3606</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0989</v>
+        <v>0.5108</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2558</v>
+        <v>-0.1502</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.1344</v>
+        <v>-0.194</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1344</v>
+        <v>-0.194</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.589</v>
+        <v>-0.2212</v>
       </c>
       <c r="T20" t="n">
-        <v>0.923</v>
+        <v>0.0345</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.334</v>
+        <v>-0.2557</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.894</v>
+        <v>1.2239</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. JIMÉNEZ BARRETO</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.248</v>
+        <v>-2.1602</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2439</v>
+        <v>-1.5866</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0041</v>
+        <v>-0.5736</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2469</v>
+        <v>0.4798</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0948</v>
+        <v>-0.5067</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1522</v>
+        <v>0.9865</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.6075</v>
+        <v>0.1252</v>
       </c>
       <c r="K21" t="n">
         <v>-0.6055</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.002</v>
+        <v>0.7307</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3606</v>
+        <v>0.3546</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5108</v>
+        <v>0.0989</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1502</v>
+        <v>0.2558</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.194</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.194</v>
+        <v>-2.1344</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0309</v>
+        <v>0.3883</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6662</v>
+        <v>0.4225</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3647</v>
+        <v>-0.0342</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2239</v>
+        <v>-0.894</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. GUEYE</t>
+          <t>J. ABRIL RAMIRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8616</v>
+        <v>-5.1807</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9443</v>
+        <v>-3.487</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9173</v>
+        <v>-1.6938</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.5902</v>
+        <v>-0.0264</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.0615</v>
+        <v>-1.4022</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5287</v>
+        <v>1.3758</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.1528</v>
+        <v>0.5989</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.5241</v>
+        <v>-0.1318</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.6287</v>
+        <v>0.7307</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4373</v>
+        <v>-0.6254</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5374</v>
+        <v>-1.2704</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1</v>
+        <v>0.645</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7761</v>
+        <v>-3.6866</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9702</v>
+        <v>-3.8806</v>
       </c>
       <c r="R22" t="n">
         <v>0.194</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8927</v>
+        <v>-0.5737</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9549</v>
+        <v>-0.2053</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0621</v>
+        <v>-0.3684</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6119</v>
+        <v>-0.894</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6119</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. ABRIL RAMIRO</t>
+          <t>S. GUEYE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8509</v>
+        <v>-5.5205</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8874</v>
+        <v>-3.1455</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9635</v>
+        <v>-2.375</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0264</v>
+        <v>-5.5902</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4022</v>
+        <v>-3.0615</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3758</v>
+        <v>-2.5287</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5989</v>
+        <v>-4.1528</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1318</v>
+        <v>-1.5241</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7307</v>
+        <v>-2.6287</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6254</v>
+        <v>-1.4373</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2704</v>
+        <v>-1.5374</v>
       </c>
       <c r="O23" t="n">
-        <v>0.645</v>
+        <v>0.1</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.6866</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R23" t="n">
         <v>0.194</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2438</v>
+        <v>0.2338</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6057</v>
+        <v>0.7537</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6381</v>
+        <v>-0.5198</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.894</v>
+        <v>0.6119</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.894</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="24">
@@ -2281,28 +2281,28 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.257699999999999</v>
+        <v>2.925099999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>3.581599999999999</v>
+        <v>3.5816</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3239</v>
+        <v>-0.6566999999999994</v>
       </c>
       <c r="G24" t="n">
-        <v>1.498299999999998</v>
+        <v>1.498299999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4202000000000001</v>
+        <v>-0.4201999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>1.918399999999999</v>
+        <v>1.918400000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>1.658599999999999</v>
+        <v>1.658600000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>3.493499999999999</v>
+        <v>3.4935</v>
       </c>
       <c r="L24" t="n">
         <v>-1.834999999999999</v>
@@ -2326,16 +2326,16 @@
         <v>3.8806</v>
       </c>
       <c r="S24" t="n">
-        <v>3.695600000000001</v>
+        <v>4.3628</v>
       </c>
       <c r="T24" t="n">
-        <v>5.775800000000001</v>
+        <v>5.775799999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.08</v>
+        <v>-1.4128</v>
       </c>
       <c r="V24" t="n">
-        <v>8.705800000000002</v>
+        <v>8.7058</v>
       </c>
       <c r="W24" t="n">
         <v>11.6699</v>
